--- a/src/Excelsior.Tests/BannerTests.NarrowColumnBannerHeightTracksActualWrap.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.NarrowColumnBannerHeightTracksActualWrap.verified.xlsx
@@ -53,7 +53,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="105" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Validation rules (enforced after upload):
@@ -70,6 +70,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:A2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:XFD1"/>
+  </mergeCells>
 </worksheet>
 </file>
 

--- a/src/Excelsior.Tests/BannerTests.NarrowColumnBannerHeightTracksActualWrap.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.NarrowColumnBannerHeightTracksActualWrap.verified.xlsx
@@ -78,7 +78,7 @@
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
 <columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
-  <sheet name="Solo" bannerRows="1">
+  <sheet name="Solo" banner="true">
     <column index="1" property="name"/>
   </sheet>
 </columnMetadata>

--- a/src/Excelsior.Tests/BannerTests.NarrowColumnBannerHeightTracksActualWrap.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.NarrowColumnBannerHeightTracksActualWrap.verified.xlsx
@@ -77,7 +77,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Solo" banner="true">
     <column index="1" property="name"/>
   </sheet>
